--- a/examples/output/NL_swissmetro_WTP.xlsx
+++ b/examples/output/NL_swissmetro_WTP.xlsx
@@ -437,22 +437,22 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>1.0490255944371714</v>
+        <v>1.0490255944369093</v>
       </c>
       <c r="C2">
-        <v>0.06733609013002989</v>
+        <v>0.0673360901299772</v>
       </c>
       <c r="D2">
-        <v>15.578950194634738</v>
+        <v>15.578950194643037</v>
       </c>
       <c r="E2">
         <v>0.0</v>
       </c>
       <c r="F2">
-        <v>0.11563817813089618</v>
+        <v>0.11563817813083746</v>
       </c>
       <c r="G2">
-        <v>9.07161986977805</v>
+        <v>9.07161986978039</v>
       </c>
       <c r="H2">
         <v>0.0</v>
